--- a/tests/fixtures/22_weekly_timesheet/pattern-by-hand-1.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/pattern-by-hand-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\2026\excel\tests\fixtures\22_weekly_timesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A1911B-E372-4986-B073-029360522C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ED54AC-8723-4291-8269-D9CBEF393ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="98">
   <si>
     <t>config:</t>
   </si>
@@ -53,27 +53,9 @@
     <t>string</t>
   </si>
   <si>
-    <t>Day of week</t>
-  </si>
-  <si>
-    <t>col_time_in</t>
-  </si>
-  <si>
-    <t>Time in</t>
-  </si>
-  <si>
     <t>col_breaks</t>
   </si>
   <si>
-    <t>Breaks\n\(minutes\)</t>
-  </si>
-  <si>
-    <t>col_time_out</t>
-  </si>
-  <si>
-    <t>Time out</t>
-  </si>
-  <si>
     <t>var:</t>
   </si>
   <si>
@@ -92,33 +74,18 @@
     <t>employee.week_starting</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>week.day</t>
-  </si>
-  <si>
     <t>datetime</t>
   </si>
   <si>
-    <t>week.time_in</t>
-  </si>
-  <si>
     <t>time</t>
   </si>
   <si>
-    <t>week.breaks</t>
-  </si>
-  <si>
     <t>integer</t>
   </si>
   <si>
     <t>\d+</t>
   </si>
   <si>
-    <t>week.time_out</t>
-  </si>
-  <si>
     <t>rate.regular</t>
   </si>
   <si>
@@ -170,15 +137,9 @@
     <t>cell:I6</t>
   </si>
   <si>
-    <t>table:*</t>
-  </si>
-  <si>
     <t>HEADER:1</t>
   </si>
   <si>
-    <t>DATA:8</t>
-  </si>
-  <si>
     <t>cell:H30</t>
   </si>
   <si>
@@ -213,6 +174,159 @@
   </si>
   <si>
     <t>END:</t>
+  </si>
+  <si>
+    <t>Day of week.*</t>
+  </si>
+  <si>
+    <t>col_time</t>
+  </si>
+  <si>
+    <t>Time.*</t>
+  </si>
+  <si>
+    <t>Regular.*</t>
+  </si>
+  <si>
+    <t>Overtime.*</t>
+  </si>
+  <si>
+    <t>Sick.*</t>
+  </si>
+  <si>
+    <t>Holiday.*</t>
+  </si>
+  <si>
+    <t>Vacation.*</t>
+  </si>
+  <si>
+    <t>Breaks.*</t>
+  </si>
+  <si>
+    <t>company.address1</t>
+  </si>
+  <si>
+    <t>company.address2</t>
+  </si>
+  <si>
+    <t>company.address3</t>
+  </si>
+  <si>
+    <t>company.phone</t>
+  </si>
+  <si>
+    <t>cell:b4</t>
+  </si>
+  <si>
+    <t>cell:b5</t>
+  </si>
+  <si>
+    <t>cell:b6</t>
+  </si>
+  <si>
+    <t>cell:b7</t>
+  </si>
+  <si>
+    <t>FOOTER:1</t>
+  </si>
+  <si>
+    <t>col_total</t>
+  </si>
+  <si>
+    <t>Total.*</t>
+  </si>
+  <si>
+    <t>col_regular</t>
+  </si>
+  <si>
+    <t>col_overtime</t>
+  </si>
+  <si>
+    <t>col_sick</t>
+  </si>
+  <si>
+    <t>col_holiday</t>
+  </si>
+  <si>
+    <t>col_vacation</t>
+  </si>
+  <si>
+    <t>doc:</t>
+  </si>
+  <si>
+    <t>read company data</t>
+  </si>
+  <si>
+    <t>read employee data</t>
+  </si>
+  <si>
+    <t>seek:b9</t>
+  </si>
+  <si>
+    <t>SKIP_IF</t>
+  </si>
+  <si>
+    <t>EMPTY</t>
+  </si>
+  <si>
+    <t>IGNORE</t>
+  </si>
+  <si>
+    <t>DATA:*</t>
+  </si>
+  <si>
+    <t>weekDay.date</t>
+  </si>
+  <si>
+    <t>weekDay.timeIn</t>
+  </si>
+  <si>
+    <t>weekDay.timeOut</t>
+  </si>
+  <si>
+    <t>weekDay.breakMinutes</t>
+  </si>
+  <si>
+    <t>weekDay.dayTotalTime</t>
+  </si>
+  <si>
+    <t>weekDay.dayRegularTime</t>
+  </si>
+  <si>
+    <t>weekDay.dayOverTime</t>
+  </si>
+  <si>
+    <t>weekDay.daySickTime</t>
+  </si>
+  <si>
+    <t>weekDay.dayHolidayTime</t>
+  </si>
+  <si>
+    <t>weekDay.dayVacationTime</t>
+  </si>
+  <si>
+    <t>weekTotal.overTime</t>
+  </si>
+  <si>
+    <t>weekTotal.sickTime</t>
+  </si>
+  <si>
+    <t>weekTotal.holidayTime</t>
+  </si>
+  <si>
+    <t>weekTotal.vacationTime</t>
+  </si>
+  <si>
+    <t>table:2</t>
+  </si>
+  <si>
+    <t>seek:i4</t>
+  </si>
+  <si>
+    <t>seek:a29</t>
+  </si>
+  <si>
+    <t>weekTotal.regularTime</t>
   </si>
 </sst>
 </file>
@@ -552,8 +666,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.06640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -566,32 +695,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
@@ -599,13 +714,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
@@ -613,436 +728,911 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
         <v>32</v>
       </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" t="s">
+        <v>6</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+      <c r="G62" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s">
+        <v>65</v>
+      </c>
+      <c r="I62" t="s">
+        <v>67</v>
+      </c>
+      <c r="J62" t="s">
+        <v>68</v>
+      </c>
+      <c r="K62" t="s">
+        <v>69</v>
+      </c>
+      <c r="L62" t="s">
+        <v>70</v>
+      </c>
+      <c r="M62" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s">
+        <v>77</v>
+      </c>
+      <c r="L63" t="s">
+        <v>77</v>
+      </c>
+      <c r="M63" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" t="s">
+        <v>83</v>
+      </c>
+      <c r="F64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s">
+        <v>77</v>
+      </c>
+      <c r="H64" t="s">
+        <v>84</v>
+      </c>
+      <c r="I64" t="s">
+        <v>85</v>
+      </c>
+      <c r="J64" t="s">
+        <v>86</v>
+      </c>
+      <c r="K64" t="s">
+        <v>87</v>
+      </c>
+      <c r="L64" t="s">
+        <v>88</v>
+      </c>
+      <c r="M64" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" t="s">
+        <v>77</v>
+      </c>
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" t="s">
+        <v>77</v>
+      </c>
+      <c r="F65" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" t="s">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s">
+        <v>65</v>
+      </c>
+      <c r="I65" t="s">
+        <v>97</v>
+      </c>
+      <c r="J65" t="s">
+        <v>90</v>
+      </c>
+      <c r="K65" t="s">
+        <v>91</v>
+      </c>
+      <c r="L65" t="s">
+        <v>92</v>
+      </c>
+      <c r="M65" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
         <v>35</v>
       </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
         <v>36</v>
       </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
         <v>37</v>
       </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="B73" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
         <v>38</v>
       </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="B74" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
         <v>39</v>
       </c>
-      <c r="C24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
+      <c r="B75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+      <c r="B76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
         <v>41</v>
       </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
         <v>42</v>
       </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
         <v>43</v>
       </c>
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
         <v>44</v>
       </c>
-      <c r="B29" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
         <v>46</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
